--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_05-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_05-01-2026.xlsx
@@ -253,7 +253,7 @@
     <t>£41.33</t>
   </si>
   <si>
-    <t>Price Not Found</t>
+    <t>£45.39</t>
   </si>
   <si>
     <t>£49.14</t>
@@ -364,16 +364,16 @@
     <t>£40.63</t>
   </si>
   <si>
+    <t>£19.80</t>
+  </si>
+  <si>
+    <t>£20.28</t>
+  </si>
+  <si>
+    <t>£24.81</t>
+  </si>
+  <si>
     <t>POA</t>
-  </si>
-  <si>
-    <t>£20.28</t>
-  </si>
-  <si>
-    <t>£24.81</t>
-  </si>
-  <si>
-    <t>£26.24</t>
   </si>
   <si>
     <t>£30.85</t>
@@ -1034,7 +1034,7 @@
         <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
@@ -1128,7 +1128,7 @@
         <v>57</v>
       </c>
       <c r="N8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
@@ -1410,7 +1410,7 @@
         <v>57</v>
       </c>
       <c r="N14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="O14" t="s">
         <v>57</v>
@@ -1551,7 +1551,7 @@
         <v>57</v>
       </c>
       <c r="N17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="O17" t="s">
         <v>71</v>

--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_05-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_05-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="89">
   <si>
     <t>SKU</t>
   </si>
@@ -232,91 +232,33 @@
     <t>POA or OOS</t>
   </si>
   <si>
-    <t>£18.75</t>
-  </si>
-  <si>
-    <t>£22.56</t>
-  </si>
-  <si>
-    <t>£26.05</t>
-  </si>
-  <si>
-    <t>£27.48</t>
-  </si>
-  <si>
-    <t>£34.23</t>
-  </si>
-  <si>
-    <t>£39.53</t>
-  </si>
-  <si>
-    <t>£41.33</t>
-  </si>
-  <si>
-    <t>£45.39</t>
-  </si>
-  <si>
-    <t>£49.14</t>
-  </si>
-  <si>
-    <t>£43.78</t>
-  </si>
-  <si>
-    <t>£63.71</t>
-  </si>
-  <si>
-    <t>£62.80</t>
-  </si>
-  <si>
-    <t>£71.35</t>
-  </si>
-  <si>
-    <t>£75.80</t>
-  </si>
-  <si>
-    <t>£77.34</t>
-  </si>
-  <si>
-    <t>£14.54</t>
-  </si>
-  <si>
-    <t>£17.48</t>
-  </si>
-  <si>
-    <t>£18.94</t>
-  </si>
-  <si>
-    <t>£23.24</t>
-  </si>
-  <si>
-    <t>£26.16</t>
-  </si>
-  <si>
-    <t>£27.24</t>
-  </si>
-  <si>
-    <t>£29.17</t>
-  </si>
-  <si>
-    <t>£32.49</t>
-  </si>
-  <si>
-    <t>£34.56</t>
-  </si>
-  <si>
-    <t>£38.66</t>
-  </si>
-  <si>
-    <t>£41.91</t>
-  </si>
-  <si>
-    <t>£48.35</t>
-  </si>
-  <si>
-    <t>£50.21</t>
-  </si>
-  <si>
-    <t>£50.55</t>
+    <t>Price Not Found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=143.0.7499.170); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff717be88e5
+	0x7ff717be8940
+	0x7ff7179c165d
+	0x7ff717a19a33
+	0x7ff717a19d3c
+	0x7ff717a6df67
+	0x7ff717a6ac97
+	0x7ff717a0ac29
+	0x7ff717a0ba93
+	0x7ff717f00640
+	0x7ff717efaf80
+	0x7ff717f196e6
+	0x7ff717c05de4
+	0x7ff717c0ed8c
+	0x7ff717bf2004
+	0x7ff717bf21b5
+	0x7ff717bd7ee2
+	0x7ff90b9ee8d7
+	0x7ff90bbcc53c
+</t>
   </si>
   <si>
     <t>£10.58</t>
@@ -362,42 +304,6 @@
   </si>
   <si>
     <t>£40.63</t>
-  </si>
-  <si>
-    <t>£19.80</t>
-  </si>
-  <si>
-    <t>£20.28</t>
-  </si>
-  <si>
-    <t>£24.81</t>
-  </si>
-  <si>
-    <t>POA</t>
-  </si>
-  <si>
-    <t>£30.85</t>
-  </si>
-  <si>
-    <t>£26.64</t>
-  </si>
-  <si>
-    <t>£38.41</t>
-  </si>
-  <si>
-    <t>£41.24</t>
-  </si>
-  <si>
-    <t>£43.58</t>
-  </si>
-  <si>
-    <t>£46.24</t>
-  </si>
-  <si>
-    <t>£51.77</t>
-  </si>
-  <si>
-    <t>£59.44</t>
   </si>
 </sst>
 </file>
@@ -840,13 +746,13 @@
         <v>57</v>
       </c>
       <c r="L2" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="M2" t="s">
         <v>57</v>
       </c>
       <c r="N2" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="O2" t="s">
         <v>71</v>
@@ -881,19 +787,19 @@
         <v>71</v>
       </c>
       <c r="J3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" t="s">
         <v>73</v>
       </c>
-      <c r="K3" t="s">
-        <v>87</v>
-      </c>
       <c r="L3" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="M3" t="s">
         <v>57</v>
       </c>
       <c r="N3" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="O3" t="s">
         <v>71</v>
@@ -928,19 +834,19 @@
         <v>71</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K4" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="L4" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="M4" t="s">
         <v>57</v>
       </c>
       <c r="N4" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
@@ -975,19 +881,19 @@
         <v>71</v>
       </c>
       <c r="J5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="L5" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="M5" t="s">
         <v>57</v>
       </c>
       <c r="N5" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
@@ -1022,19 +928,19 @@
         <v>71</v>
       </c>
       <c r="J6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K6" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="L6" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="M6" t="s">
         <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
@@ -1069,19 +975,19 @@
         <v>71</v>
       </c>
       <c r="J7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K7" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="L7" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="M7" t="s">
         <v>57</v>
       </c>
       <c r="N7" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
@@ -1116,19 +1022,19 @@
         <v>71</v>
       </c>
       <c r="J8" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K8" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="L8" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="M8" t="s">
         <v>57</v>
       </c>
       <c r="N8" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
@@ -1163,19 +1069,19 @@
         <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K9" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="L9" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="M9" t="s">
         <v>57</v>
       </c>
       <c r="N9" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="O9" t="s">
         <v>71</v>
@@ -1210,19 +1116,19 @@
         <v>71</v>
       </c>
       <c r="J10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="L10" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="M10" t="s">
         <v>57</v>
       </c>
       <c r="N10" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="O10" t="s">
         <v>71</v>
@@ -1257,19 +1163,19 @@
         <v>71</v>
       </c>
       <c r="J11" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K11" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="L11" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="M11" t="s">
         <v>57</v>
       </c>
       <c r="N11" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="O11" t="s">
         <v>71</v>
@@ -1304,19 +1210,19 @@
         <v>71</v>
       </c>
       <c r="J12" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="K12" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="L12" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="M12" t="s">
         <v>57</v>
       </c>
       <c r="N12" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="O12" t="s">
         <v>71</v>
@@ -1351,19 +1257,19 @@
         <v>71</v>
       </c>
       <c r="J13" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="K13" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L13" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="M13" t="s">
         <v>57</v>
       </c>
       <c r="N13" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="O13" t="s">
         <v>71</v>
@@ -1410,7 +1316,7 @@
         <v>57</v>
       </c>
       <c r="N14" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="O14" t="s">
         <v>57</v>
@@ -1445,19 +1351,19 @@
         <v>71</v>
       </c>
       <c r="J15" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="K15" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="L15" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="M15" t="s">
         <v>57</v>
       </c>
       <c r="N15" t="s">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="O15" t="s">
         <v>71</v>
@@ -1492,19 +1398,19 @@
         <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="K16" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="L16" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="M16" t="s">
         <v>57</v>
       </c>
       <c r="N16" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="O16" t="s">
         <v>71</v>
@@ -1539,19 +1445,19 @@
         <v>71</v>
       </c>
       <c r="J17" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="K17" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="L17" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="M17" t="s">
         <v>57</v>
       </c>
       <c r="N17" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="O17" t="s">
         <v>71</v>
